--- a/01-projetos/01-data-project-foundations/data/input/absenteeism_data_10.xlsx
+++ b/01-projetos/01-data-project-foundations/data/input/absenteeism_data_10.xlsx
@@ -471,74 +471,74 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>75569</v>
+        <v>83397</v>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Vicente Campos</t>
+          <t>Ana Beatriz Gomes</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Atendimento ao Cliente</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E2" t="n">
         <v>4</v>
       </c>
       <c r="F2" s="2" t="n">
-        <v>45098</v>
+        <v>45093</v>
       </c>
       <c r="G2" t="n">
-        <v>5236.81</v>
+        <v>11706.39</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>34782</v>
+        <v>16018</v>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Sra. Manuela Alves</t>
+          <t>Sra. Gabriela Dias</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Jurídico</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F3" s="2" t="n">
-        <v>45079</v>
+        <v>45090</v>
       </c>
       <c r="G3" t="n">
-        <v>8813.889999999999</v>
+        <v>11612.64</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>29543</v>
+        <v>73495</v>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ana Carolina Silva</t>
+          <t>Ana Vitória Gonçalves</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>TI</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -547,85 +547,85 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F4" s="2" t="n">
-        <v>45084</v>
+        <v>45086</v>
       </c>
       <c r="G4" t="n">
-        <v>8595.02</v>
+        <v>6671.84</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>65723</v>
+        <v>442</v>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Sr. Henrique Correia</t>
+          <t>Srta. Clara Aragão</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Doença</t>
+          <t>Viagem de negócios</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>45078</v>
+        <v>45105</v>
       </c>
       <c r="G5" t="n">
-        <v>11750.43</v>
+        <v>4742.68</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>13303</v>
+        <v>81565</v>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Isis Fernandes</t>
+          <t>João Pereira</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Vendas</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F6" s="2" t="n">
-        <v>45104</v>
+        <v>45099</v>
       </c>
       <c r="G6" t="n">
-        <v>9790.530000000001</v>
+        <v>8915.870000000001</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>44074</v>
+        <v>7132</v>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>André Costela</t>
+          <t>Benjamin Nogueira</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Financeiro</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -634,129 +634,129 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>45102</v>
+        <v>45092</v>
       </c>
       <c r="G7" t="n">
-        <v>7653.43</v>
+        <v>7903.98</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>91779</v>
+        <v>41973</v>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Luiz Fernando Farias</t>
+          <t>Sra. Milena Fernandes</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Vendas</t>
+          <t>Financeiro</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Problemas pessoais</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>45089</v>
+        <v>45083</v>
       </c>
       <c r="G8" t="n">
-        <v>10326.67</v>
+        <v>7807.91</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>67844</v>
+        <v>1796</v>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Camila da Cruz</t>
+          <t>Isabelly Ribeiro</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Jurídico</t>
+          <t>P&amp;D</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>45093</v>
+        <v>45085</v>
       </c>
       <c r="G9" t="n">
-        <v>4937.24</v>
+        <v>6630.86</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>58123</v>
+        <v>24282</v>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Melissa Silveira</t>
+          <t>Levi Souza</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>P&amp;D</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Consulta médica</t>
+          <t>Doença</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>45090</v>
+        <v>45093</v>
       </c>
       <c r="G10" t="n">
-        <v>6637.48</v>
+        <v>5316.65</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>35809</v>
+        <v>66991</v>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Lavínia Vieira</t>
+          <t>Paulo Silva</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Engenharia</t>
+          <t>Recursos Humanos</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Outros</t>
+          <t>Problemas pessoais</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>45078</v>
+        <v>45099</v>
       </c>
       <c r="G11" t="n">
-        <v>11046.88</v>
+        <v>7446.99</v>
       </c>
     </row>
   </sheetData>
